--- a/Ders_Programi.xlsx
+++ b/Ders_Programi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erbakanedutr-my.sharepoint.com/personal/24830602764_erbakan_edu_tr/Documents/KODLAMA/Proje/Proje Tabanlı Ders işleme/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{51043090-FB29-42CB-8E50-FFF0519A14EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41BAB8E8-7D83-4074-951D-CC9993B78B6E}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{51043090-FB29-42CB-8E50-FFF0519A14EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2131F13E-B8FB-496E-B38B-A05603FE0BC6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="13">
   <si>
     <t>Gün</t>
   </si>
@@ -37,10 +37,28 @@
     <t>Perşembe</t>
   </si>
   <si>
-    <t>8-A Fen</t>
-  </si>
-  <si>
-    <t>8-B Fen</t>
+    <t>Pazartesi</t>
+  </si>
+  <si>
+    <t>7-D Fen</t>
+  </si>
+  <si>
+    <t>7-D Rehb</t>
+  </si>
+  <si>
+    <t>Salı</t>
+  </si>
+  <si>
+    <t>7-B Fen</t>
+  </si>
+  <si>
+    <t>7-C Fen</t>
+  </si>
+  <si>
+    <t>7-A Fen</t>
+  </si>
+  <si>
+    <t>7-E Fen</t>
   </si>
 </sst>
 </file>
@@ -424,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -440,97 +458,238 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>0.38194444444444442</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1">
-        <v>0.41666666666666669</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>0.52083333333333337</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1">
-        <v>0.38194444444444442</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1">
-        <v>0.41666666666666669</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>0.4513888888888889</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.58680555555555558</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="1">
-        <v>0.4861111111111111</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
+      <c r="B17" s="1">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0.58680555555555558</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="1">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C22" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:C1" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Ders_Programi.xlsx
+++ b/Ders_Programi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erbakanedutr-my.sharepoint.com/personal/24830602764_erbakan_edu_tr/Documents/KODLAMA/Proje/Proje Tabanlı Ders işleme/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{51043090-FB29-42CB-8E50-FFF0519A14EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2131F13E-B8FB-496E-B38B-A05603FE0BC6}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{51043090-FB29-42CB-8E50-FFF0519A14EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{146ED2CF-A9C2-4B3B-9505-A8D1A65A64CE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,9 +43,6 @@
     <t>7-D Fen</t>
   </si>
   <si>
-    <t>7-D Rehb</t>
-  </si>
-  <si>
     <t>Salı</t>
   </si>
   <si>
@@ -59,6 +56,9 @@
   </si>
   <si>
     <t>7-E Fen</t>
+  </si>
+  <si>
+    <t>7-D Reh</t>
   </si>
 </sst>
 </file>
@@ -486,73 +486,73 @@
         <v>0.49305555555555558</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1">
         <v>0.35416666666666669</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
         <v>0.3888888888888889</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1">
         <v>0.4236111111111111</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1">
         <v>0.45833333333333331</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1">
         <v>0.49305555555555558</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1">
         <v>0.54861111111111116</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -563,7 +563,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -574,7 +574,7 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -585,7 +585,7 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -596,7 +596,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -607,7 +607,7 @@
         <v>0.54861111111111116</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -618,7 +618,7 @@
         <v>0.58680555555555558</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -629,7 +629,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -640,7 +640,7 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -651,7 +651,7 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -662,7 +662,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">

--- a/Ders_Programi.xlsx
+++ b/Ders_Programi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erbakanedutr-my.sharepoint.com/personal/24830602764_erbakan_edu_tr/Documents/KODLAMA/Proje/Proje Tabanlı Ders işleme/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{51043090-FB29-42CB-8E50-FFF0519A14EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{146ED2CF-A9C2-4B3B-9505-A8D1A65A64CE}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{51043090-FB29-42CB-8E50-FFF0519A14EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C1E9357-1CD5-4DB8-9420-CB87CDE69896}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="23355" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -461,7 +461,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>0.35416666666666669</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -472,7 +472,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1">
-        <v>0.3888888888888889</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -486,18 +486,18 @@
         <v>0.49305555555555558</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>0.35416666666666669</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -505,7 +505,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="1">
-        <v>0.3888888888888889</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -516,10 +516,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>0.4236111111111111</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -527,7 +527,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>0.45833333333333331</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -538,10 +538,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="1">
-        <v>0.49305555555555558</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -549,21 +549,21 @@
         <v>7</v>
       </c>
       <c r="B10" s="1">
-        <v>0.54861111111111116</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1">
-        <v>0.35416666666666669</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -571,10 +571,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="1">
-        <v>0.3888888888888889</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -582,10 +582,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="1">
-        <v>0.4236111111111111</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -593,10 +593,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="1">
-        <v>0.45833333333333331</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -604,10 +604,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="1">
-        <v>0.54861111111111116</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -618,7 +618,7 @@
         <v>0.58680555555555558</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -629,7 +629,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -640,7 +640,7 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -651,7 +651,7 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -662,7 +662,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -670,10 +670,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="1">
-        <v>0.58680555555555558</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -681,10 +681,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="1">
-        <v>0.61458333333333337</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Ders_Programi.xlsx
+++ b/Ders_Programi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erbakanedutr-my.sharepoint.com/personal/24830602764_erbakan_edu_tr/Documents/KODLAMA/Proje/Proje Tabanlı Ders işleme/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{51043090-FB29-42CB-8E50-FFF0519A14EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C1E9357-1CD5-4DB8-9420-CB87CDE69896}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{51043090-FB29-42CB-8E50-FFF0519A14EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0576DB24-4293-48DE-9581-3EAF926A2496}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="23355" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
